--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B68AE126-7A41-4C27-8DF4-72FF84AC8D71}"/>
+  <xr:revisionPtr revIDLastSave="328" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9229329-714C-4A9A-B36B-E912AFB968E6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>tired!</t>
+  </si>
+  <si>
+    <t>6.09.2026</t>
   </si>
 </sst>
 </file>
@@ -2274,26 +2277,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>60</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>90</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="328" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9229329-714C-4A9A-B36B-E912AFB968E6}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9213927A-4FBE-4B5D-AC30-C3504333480E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,15 @@
   </si>
   <si>
     <t>6.09.2026</t>
+  </si>
+  <si>
+    <t>7.09.2026</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>tired!!</t>
   </si>
 </sst>
 </file>
@@ -2323,26 +2332,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>30</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9213927A-4FBE-4B5D-AC30-C3504333480E}"/>
+  <xr:revisionPtr revIDLastSave="352" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52C330C1-1213-402F-A8F3-B59F311A4C38}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>tired!!</t>
+  </si>
+  <si>
+    <t>8.09.2026</t>
   </si>
 </sst>
 </file>
@@ -2378,26 +2381,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>60</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>30</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52C330C1-1213-402F-A8F3-B59F311A4C38}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F39B9F71-0441-4B2D-B1E8-2FF2659B4D3C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>8.09.2026</t>
+  </si>
+  <si>
+    <t>9.09.2026</t>
   </si>
 </sst>
 </file>
@@ -648,6 +651,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2427,26 +2434,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>6</v>
+      </c>
+      <c r="H34" s="14">
+        <v>30</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F39B9F71-0441-4B2D-B1E8-2FF2659B4D3C}"/>
+  <xr:revisionPtr revIDLastSave="376" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96237891-D06D-44A7-BA4A-BBDF9DBB1A60}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,12 @@
   </si>
   <si>
     <t>9.09.2026</t>
+  </si>
+  <si>
+    <t>10.09.2026</t>
+  </si>
+  <si>
+    <t>great day!</t>
   </si>
 </sst>
 </file>
@@ -651,10 +657,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2480,26 +2482,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>60</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>30</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="376" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96237891-D06D-44A7-BA4A-BBDF9DBB1A60}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA832BE-B6E4-45D9-BA10-0FD8CCF27BCB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>great day!</t>
+  </si>
+  <si>
+    <t>11.09.2026</t>
+  </si>
+  <si>
+    <t>very tired.</t>
   </si>
 </sst>
 </file>
@@ -657,6 +663,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2528,26 +2538,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="14">
+        <v>480</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>180</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA832BE-B6E4-45D9-BA10-0FD8CCF27BCB}"/>
+  <xr:revisionPtr revIDLastSave="402" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20FF347F-2766-425D-9D5E-D92A750C184B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t>very tired.</t>
+  </si>
+  <si>
+    <t>12.09.2026</t>
+  </si>
+  <si>
+    <t>weekend finally!</t>
   </si>
 </sst>
 </file>
@@ -663,10 +669,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2584,26 +2586,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>240</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="402" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20FF347F-2766-425D-9D5E-D92A750C184B}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A979DD-475A-4C30-85F5-0A0C80CD128A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>weekend finally!</t>
+  </si>
+  <si>
+    <t>13.09.2026</t>
+  </si>
+  <si>
+    <t>exhausted!</t>
   </si>
 </sst>
 </file>
@@ -669,6 +675,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2632,26 +2642,46 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="D38" s="14">
+        <v>90</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>240</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>1050</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="412" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A979DD-475A-4C30-85F5-0A0C80CD128A}"/>
+  <xr:revisionPtr revIDLastSave="426" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C67D9C0D-F9D1-4230-8089-A42BEE0B099F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="122">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>exhausted!</t>
+  </si>
+  <si>
+    <t>14.09.2026</t>
+  </si>
+  <si>
+    <t>back to back exams!!</t>
   </si>
 </sst>
 </file>
@@ -2645,8 +2651,12 @@
       <c r="A38" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
+      <c r="B38" s="14">
+        <v>480</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
       <c r="D38" s="14">
         <v>90</v>
       </c>
@@ -2664,11 +2674,11 @@
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>390</v>
+        <v>900</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>1050</v>
+        <v>540</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>61</v>
@@ -2684,26 +2694,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="14">
+        <v>480</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>250</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>180</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="426" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C67D9C0D-F9D1-4230-8089-A42BEE0B099F}"/>
+  <xr:revisionPtr revIDLastSave="438" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90283660-29CE-4347-9C86-0139C578BB6D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>back to back exams!!</t>
+  </si>
+  <si>
+    <t>15.09.2026</t>
   </si>
 </sst>
 </file>
@@ -2740,26 +2743,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="14">
+        <v>480</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>90</v>
+      </c>
+      <c r="E40" s="14">
+        <v>90</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>180</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="438" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90283660-29CE-4347-9C86-0139C578BB6D}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689CAB97-750E-40D9-9286-D9F41CA3452D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -404,6 +404,12 @@
   </si>
   <si>
     <t>15.09.2026</t>
+  </si>
+  <si>
+    <t>16.09.2026</t>
+  </si>
+  <si>
+    <t>studying!</t>
   </si>
 </sst>
 </file>
@@ -2789,26 +2795,48 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
+      <c r="A41" s="13" t="s">
+        <v>123</v>
+      </c>
       <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>90</v>
+      </c>
+      <c r="E41" s="14">
+        <v>90</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>120</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="449" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689CAB97-750E-40D9-9286-D9F41CA3452D}"/>
+  <xr:revisionPtr revIDLastSave="460" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E4BEB1E-9E0D-437F-B353-2ED7DF340674}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="127">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -410,6 +410,12 @@
   </si>
   <si>
     <t>studying!</t>
+  </si>
+  <si>
+    <t>17.09.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A good day with less classes!</t>
   </si>
 </sst>
 </file>
@@ -2839,26 +2845,46 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
+      <c r="A42" s="13" t="s">
+        <v>125</v>
+      </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="D42" s="14">
+        <v>90</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>150</v>
+      </c>
+      <c r="G42" s="14">
+        <v>3</v>
+      </c>
+      <c r="H42" s="14">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>1020</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E4BEB1E-9E0D-437F-B353-2ED7DF340674}"/>
+  <xr:revisionPtr revIDLastSave="475" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C520445D-8CA1-4752-B1F9-6CE736E061C6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="129">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -416,6 +416,12 @@
   </si>
   <si>
     <t xml:space="preserve"> A good day with less classes!</t>
+  </si>
+  <si>
+    <t>18.09.2026</t>
+  </si>
+  <si>
+    <t>stressed!</t>
   </si>
 </sst>
 </file>
@@ -2804,7 +2810,9 @@
       <c r="A41" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B41" s="14"/>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
       <c r="C41" s="14">
         <v>30</v>
       </c>
@@ -2825,11 +2833,11 @@
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>1050</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>390</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>61</v>
@@ -2848,8 +2856,12 @@
       <c r="A42" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
       <c r="D42" s="14">
         <v>90</v>
       </c>
@@ -2867,11 +2879,11 @@
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>870</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>570</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>61</v>
@@ -2887,26 +2899,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>30</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="475" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C520445D-8CA1-4752-B1F9-6CE736E061C6}"/>
+  <xr:revisionPtr revIDLastSave="487" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5181EF1E-9AE4-4106-9957-99B42BF12AC7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -422,6 +422,9 @@
   </si>
   <si>
     <t>stressed!</t>
+  </si>
+  <si>
+    <t>19.09.2026</t>
   </si>
 </sst>
 </file>
@@ -2945,25 +2948,47 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="487" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5181EF1E-9AE4-4106-9957-99B42BF12AC7}"/>
+  <xr:revisionPtr revIDLastSave="500" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06D4E26B-5630-4A90-9640-FE15F864F3DF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="131">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -425,6 +425,9 @@
   </si>
   <si>
     <t>19.09.2026</t>
+  </si>
+  <si>
+    <t>20.09.2026</t>
   </si>
 </sst>
 </file>
@@ -2992,26 +2995,50 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="14">
+        <v>540</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>60</v>
+      </c>
+      <c r="E45" s="14">
+        <v>30</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>180</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="500" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06D4E26B-5630-4A90-9640-FE15F864F3DF}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CA5C66D-BA3B-4BB6-B6DB-B842E4FD4C7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -428,6 +428,12 @@
   </si>
   <si>
     <t>20.09.2026</t>
+  </si>
+  <si>
+    <t>21.09.2026</t>
+  </si>
+  <si>
+    <t>A good day!</t>
   </si>
 </sst>
 </file>
@@ -708,10 +714,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3041,26 +3043,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>60</v>
+      </c>
+      <c r="E46" s="14">
+        <v>30</v>
+      </c>
+      <c r="F46" s="14">
+        <v>250</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>180</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CA5C66D-BA3B-4BB6-B6DB-B842E4FD4C7D}"/>
+  <xr:revisionPtr revIDLastSave="525" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B75A20F3-8C00-42B0-A9FC-EC417F8FD438}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="135">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -434,6 +434,12 @@
   </si>
   <si>
     <t>A good day!</t>
+  </si>
+  <si>
+    <t>22.09.2026</t>
+  </si>
+  <si>
+    <t>fine I guess!</t>
   </si>
 </sst>
 </file>
@@ -714,6 +720,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3089,26 +3099,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="14">
+        <v>360</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>60</v>
+      </c>
+      <c r="E47" s="14">
+        <v>30</v>
+      </c>
+      <c r="F47" s="14">
+        <v>350</v>
+      </c>
+      <c r="G47" s="14">
+        <v>7</v>
+      </c>
+      <c r="H47" s="14">
+        <v>180</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="525" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B75A20F3-8C00-42B0-A9FC-EC417F8FD438}"/>
+  <xr:revisionPtr revIDLastSave="536" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A70B2B7-B2B2-469B-AECE-001B9E9FD70B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="137">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -439,7 +439,13 @@
     <t>22.09.2026</t>
   </si>
   <si>
-    <t>fine I guess!</t>
+    <t>23.09.2026</t>
+  </si>
+  <si>
+    <t>fine  guess!</t>
+  </si>
+  <si>
+    <t>exams ahead!</t>
   </si>
 </sst>
 </file>
@@ -3141,30 +3147,50 @@
         <v>56</v>
       </c>
       <c r="N47" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="D48" s="14">
+        <v>60</v>
+      </c>
+      <c r="E48" s="14">
+        <v>30</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>180</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>870</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="536" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A70B2B7-B2B2-469B-AECE-001B9E9FD70B}"/>
+  <xr:revisionPtr revIDLastSave="551" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32654384-9D4E-4E4C-BBDA-0842E81FBC85}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="139">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -446,6 +446,12 @@
   </si>
   <si>
     <t>exams ahead!</t>
+  </si>
+  <si>
+    <t>24.09.2026</t>
+  </si>
+  <si>
+    <t>only 2 classes today!!</t>
   </si>
 </sst>
 </file>
@@ -3154,8 +3160,12 @@
       <c r="A48" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
+      <c r="B48" s="14">
+        <v>420</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
       <c r="D48" s="14">
         <v>60</v>
       </c>
@@ -3173,11 +3183,11 @@
       </c>
       <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v>570</v>
+        <v>1020</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v>870</v>
+        <v>420</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>55</v>
@@ -3193,26 +3203,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>60</v>
+      </c>
+      <c r="E49" s="14">
+        <v>30</v>
+      </c>
+      <c r="F49" s="14">
+        <v>100</v>
+      </c>
+      <c r="G49" s="14">
+        <v>2</v>
+      </c>
+      <c r="H49" s="14">
+        <v>180</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="551" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32654384-9D4E-4E4C-BBDA-0842E81FBC85}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4727C25-F8DE-437F-8B41-BC1328462EC7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -452,6 +452,12 @@
   </si>
   <si>
     <t>only 2 classes today!!</t>
+  </si>
+  <si>
+    <t>25.09.2026</t>
+  </si>
+  <si>
+    <t>relaxed!</t>
   </si>
 </sst>
 </file>
@@ -3249,26 +3255,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="14">
+        <v>420</v>
+      </c>
+      <c r="C50" s="14">
+        <v>30</v>
+      </c>
+      <c r="D50" s="14">
+        <v>60</v>
+      </c>
+      <c r="E50" s="14">
+        <v>30</v>
+      </c>
+      <c r="F50" s="14">
+        <v>300</v>
+      </c>
+      <c r="G50" s="14">
+        <v>6</v>
+      </c>
+      <c r="H50" s="14">
+        <v>180</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4727C25-F8DE-437F-8B41-BC1328462EC7}"/>
+  <xr:revisionPtr revIDLastSave="576" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0CFFB93-5D5E-498E-9C68-49170D3E05C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="143">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -458,6 +458,12 @@
   </si>
   <si>
     <t>relaxed!</t>
+  </si>
+  <si>
+    <t>26.09.2026</t>
+  </si>
+  <si>
+    <t>mid term ahead!</t>
   </si>
 </sst>
 </file>
@@ -3301,26 +3307,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>120</v>
+      </c>
+      <c r="E51" s="14">
+        <v>90</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>180</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="576" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0CFFB93-5D5E-498E-9C68-49170D3E05C4}"/>
+  <xr:revisionPtr revIDLastSave="589" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F350A1-556E-4206-8794-6D0E4441B41D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="145">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -464,6 +464,12 @@
   </si>
   <si>
     <t>mid term ahead!</t>
+  </si>
+  <si>
+    <t>27.09.2026</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -3352,26 +3358,48 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="14">
+        <v>360</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>120</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>930</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="589" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F350A1-556E-4206-8794-6D0E4441B41D}"/>
+  <xr:revisionPtr revIDLastSave="950" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E08AF17-15D3-4CF5-81DE-D647701F525A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="178">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -470,6 +470,105 @@
   </si>
   <si>
     <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>28.09.2026</t>
+  </si>
+  <si>
+    <t>29.09.2026</t>
+  </si>
+  <si>
+    <t>30.09.2026</t>
+  </si>
+  <si>
+    <t>1.10.2026</t>
+  </si>
+  <si>
+    <t>finally reached home!!</t>
+  </si>
+  <si>
+    <t>2.10.2026</t>
+  </si>
+  <si>
+    <t>3.10.2026</t>
+  </si>
+  <si>
+    <t>4.10.2026</t>
+  </si>
+  <si>
+    <t>5.10.2026</t>
+  </si>
+  <si>
+    <t>attending online classes!</t>
+  </si>
+  <si>
+    <t>6.10.2026</t>
+  </si>
+  <si>
+    <t>7.10.2026</t>
+  </si>
+  <si>
+    <t>8.10.2026</t>
+  </si>
+  <si>
+    <t>9.10.2026</t>
+  </si>
+  <si>
+    <t>10.10.2026</t>
+  </si>
+  <si>
+    <t>11.10.2026</t>
+  </si>
+  <si>
+    <t>12.10.2026</t>
+  </si>
+  <si>
+    <t>13.10.2026</t>
+  </si>
+  <si>
+    <t>14.10.2026</t>
+  </si>
+  <si>
+    <t>15.10.2026</t>
+  </si>
+  <si>
+    <t>16.10.2026</t>
+  </si>
+  <si>
+    <t>17.10.2026</t>
+  </si>
+  <si>
+    <t>18.10.2026</t>
+  </si>
+  <si>
+    <t>19.10.2026</t>
+  </si>
+  <si>
+    <t>20.10.2026</t>
+  </si>
+  <si>
+    <t>21.10.2026</t>
+  </si>
+  <si>
+    <t>22.10.2026</t>
+  </si>
+  <si>
+    <t>23.10.2026</t>
+  </si>
+  <si>
+    <t>24.10.2026</t>
+  </si>
+  <si>
+    <t>25.10.2026</t>
+  </si>
+  <si>
+    <t>26.10.2026</t>
+  </si>
+  <si>
+    <t>27.10.2026</t>
+  </si>
+  <si>
+    <t>28.10.2026</t>
   </si>
 </sst>
 </file>
@@ -3403,685 +3502,1371 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="14">
+        <v>420</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>870</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B54" s="14">
+        <v>420</v>
+      </c>
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>120</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B55" s="14">
+        <v>480</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>240</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B56" s="14">
+        <v>480</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>240</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" s="14">
+        <v>480</v>
+      </c>
+      <c r="C57" s="14">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>240</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B58" s="14">
+        <v>480</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>90</v>
+      </c>
+      <c r="E58" s="14">
+        <v>30</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>240</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" s="14">
+        <v>480</v>
+      </c>
+      <c r="C59" s="14">
+        <v>60</v>
+      </c>
+      <c r="D59" s="14">
+        <v>90</v>
+      </c>
+      <c r="E59" s="14">
+        <v>60</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>240</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>60</v>
+      </c>
+      <c r="D60" s="14">
+        <v>90</v>
+      </c>
+      <c r="E60" s="14">
+        <v>60</v>
+      </c>
+      <c r="F60" s="14">
+        <v>250</v>
+      </c>
+      <c r="G60" s="14">
+        <v>5</v>
+      </c>
+      <c r="H60" s="14">
+        <v>240</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" s="14">
+        <v>420</v>
+      </c>
+      <c r="C61" s="14">
+        <v>60</v>
+      </c>
+      <c r="D61" s="14">
+        <v>90</v>
+      </c>
+      <c r="E61" s="14">
+        <v>60</v>
+      </c>
+      <c r="F61" s="14">
+        <v>350</v>
+      </c>
+      <c r="G61" s="14">
+        <v>7</v>
+      </c>
+      <c r="H61" s="14">
+        <v>240</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B62" s="14">
+        <v>480</v>
+      </c>
+      <c r="C62" s="14">
+        <v>90</v>
+      </c>
+      <c r="D62" s="14">
+        <v>90</v>
+      </c>
+      <c r="E62" s="14">
+        <v>60</v>
+      </c>
+      <c r="F62" s="14">
+        <v>300</v>
+      </c>
+      <c r="G62" s="14">
+        <v>6</v>
+      </c>
+      <c r="H62" s="14">
+        <v>240</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B63" s="14">
+        <v>420</v>
+      </c>
+      <c r="C63" s="14">
+        <v>90</v>
+      </c>
+      <c r="D63" s="14">
+        <v>90</v>
+      </c>
+      <c r="E63" s="14">
+        <v>60</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>240</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" s="14">
+        <v>480</v>
+      </c>
+      <c r="C64" s="14">
+        <v>90</v>
+      </c>
+      <c r="D64" s="14">
+        <v>90</v>
+      </c>
+      <c r="E64" s="14">
+        <v>60</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>240</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B65" s="14">
+        <v>480</v>
+      </c>
+      <c r="C65" s="14">
+        <v>90</v>
+      </c>
+      <c r="D65" s="14">
+        <v>60</v>
+      </c>
+      <c r="E65" s="14">
+        <v>60</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>240</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B66" s="14">
+        <v>420</v>
+      </c>
+      <c r="C66" s="14">
+        <v>90</v>
+      </c>
+      <c r="D66" s="14">
+        <v>60</v>
+      </c>
+      <c r="E66" s="14">
+        <v>60</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>240</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>90</v>
+      </c>
+      <c r="D67" s="14">
+        <v>60</v>
+      </c>
+      <c r="E67" s="14">
+        <v>60</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>240</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B68" s="14">
+        <v>480</v>
+      </c>
+      <c r="C68" s="14">
+        <v>90</v>
+      </c>
+      <c r="D68" s="14">
+        <v>60</v>
+      </c>
+      <c r="E68" s="14">
+        <v>60</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>240</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="14">
+        <v>480</v>
+      </c>
+      <c r="C69" s="14">
+        <v>90</v>
+      </c>
+      <c r="D69" s="14">
+        <v>60</v>
+      </c>
+      <c r="E69" s="14">
+        <v>60</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>180</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" s="14">
+        <v>420</v>
+      </c>
+      <c r="C70" s="14">
+        <v>60</v>
+      </c>
+      <c r="D70" s="14">
+        <v>90</v>
+      </c>
+      <c r="E70" s="14">
+        <v>90</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>180</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B71" s="14">
+        <v>420</v>
+      </c>
+      <c r="C71" s="14">
+        <v>90</v>
+      </c>
+      <c r="D71" s="14">
+        <v>60</v>
+      </c>
+      <c r="E71" s="14">
+        <v>60</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>180</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" s="14">
+        <v>420</v>
+      </c>
+      <c r="C72" s="14">
+        <v>60</v>
+      </c>
+      <c r="D72" s="14">
+        <v>60</v>
+      </c>
+      <c r="E72" s="14">
+        <v>60</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>180</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="14">
+        <v>480</v>
+      </c>
+      <c r="C73" s="14">
+        <v>0</v>
+      </c>
+      <c r="D73" s="14">
+        <v>0</v>
+      </c>
+      <c r="E73" s="14">
+        <v>0</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>240</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" s="14">
+        <v>480</v>
+      </c>
+      <c r="C74" s="14">
+        <v>0</v>
+      </c>
+      <c r="D74" s="14">
+        <v>0</v>
+      </c>
+      <c r="E74" s="14">
+        <v>0</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>180</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B75" s="14">
+        <v>420</v>
+      </c>
+      <c r="C75" s="14">
+        <v>0</v>
+      </c>
+      <c r="D75" s="14">
+        <v>0</v>
+      </c>
+      <c r="E75" s="14">
+        <v>0</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>180</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
+        <v>840</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="14">
+        <v>420</v>
+      </c>
+      <c r="C76" s="14">
+        <v>30</v>
+      </c>
+      <c r="D76" s="14">
+        <v>60</v>
+      </c>
+      <c r="E76" s="14">
+        <v>60</v>
+      </c>
+      <c r="F76" s="14">
+        <v>300</v>
+      </c>
+      <c r="G76" s="14">
+        <v>6</v>
+      </c>
+      <c r="H76" s="14">
+        <v>180</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="14">
+        <v>480</v>
+      </c>
+      <c r="C77" s="14">
+        <v>30</v>
+      </c>
+      <c r="D77" s="14">
+        <v>60</v>
+      </c>
+      <c r="E77" s="14">
+        <v>60</v>
+      </c>
+      <c r="F77" s="14">
+        <v>150</v>
+      </c>
+      <c r="G77" s="14">
+        <v>3</v>
+      </c>
+      <c r="H77" s="14">
+        <v>120</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="14">
+        <v>420</v>
+      </c>
+      <c r="C78" s="14">
+        <v>30</v>
+      </c>
+      <c r="D78" s="14">
+        <v>60</v>
+      </c>
+      <c r="E78" s="14">
+        <v>60</v>
+      </c>
+      <c r="F78" s="14">
+        <v>300</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6</v>
+      </c>
+      <c r="H78" s="14">
+        <v>120</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B79" s="14">
+        <v>480</v>
+      </c>
+      <c r="C79" s="14">
+        <v>30</v>
+      </c>
+      <c r="D79" s="14">
+        <v>60</v>
+      </c>
+      <c r="E79" s="14">
+        <v>60</v>
+      </c>
+      <c r="F79" s="14">
+        <v>200</v>
+      </c>
+      <c r="G79" s="14">
+        <v>4</v>
+      </c>
+      <c r="H79" s="14">
+        <v>120</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B80" s="14">
+        <v>360</v>
+      </c>
+      <c r="C80" s="14">
+        <v>30</v>
+      </c>
+      <c r="D80" s="14">
+        <v>60</v>
+      </c>
+      <c r="E80" s="14">
+        <v>60</v>
+      </c>
+      <c r="F80" s="14">
+        <v>0</v>
+      </c>
+      <c r="G80" s="14">
+        <v>0</v>
+      </c>
+      <c r="H80" s="14">
+        <v>120</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
+        <v>810</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B81" s="14">
+        <v>420</v>
+      </c>
+      <c r="C81" s="14">
+        <v>30</v>
+      </c>
+      <c r="D81" s="14">
+        <v>90</v>
+      </c>
+      <c r="E81" s="14">
+        <v>60</v>
+      </c>
+      <c r="F81" s="14">
+        <v>250</v>
+      </c>
+      <c r="G81" s="14">
+        <v>5</v>
+      </c>
+      <c r="H81" s="14">
+        <v>150</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+      <c r="A82" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B82" s="14">
+        <v>480</v>
+      </c>
+      <c r="C82" s="14">
+        <v>30</v>
+      </c>
+      <c r="D82" s="14">
+        <v>60</v>
+      </c>
+      <c r="E82" s="14">
+        <v>60</v>
+      </c>
+      <c r="F82" s="14">
+        <v>350</v>
+      </c>
+      <c r="G82" s="14">
+        <v>7</v>
+      </c>
+      <c r="H82" s="14">
+        <v>120</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+      <c r="A83" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B83" s="14">
+        <v>480</v>
+      </c>
+      <c r="C83" s="14">
+        <v>30</v>
+      </c>
+      <c r="D83" s="14">
+        <v>60</v>
+      </c>
+      <c r="E83" s="14">
+        <v>60</v>
+      </c>
+      <c r="F83" s="14">
+        <v>300</v>
+      </c>
+      <c r="G83" s="14">
+        <v>6</v>
+      </c>
+      <c r="H83" s="14">
+        <v>60</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="950" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E08AF17-15D3-4CF5-81DE-D647701F525A}"/>
+  <xr:revisionPtr revIDLastSave="962" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26F843E6-E690-489A-B3A3-64107046BB83}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="179">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -569,6 +569,9 @@
   </si>
   <si>
     <t>28.10.2026</t>
+  </si>
+  <si>
+    <t>29.10.2026</t>
   </si>
 </sst>
 </file>
@@ -4870,25 +4873,47 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+      <c r="A84" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" s="14">
+        <v>420</v>
+      </c>
+      <c r="C84" s="14">
+        <v>30</v>
+      </c>
+      <c r="D84" s="14">
+        <v>60</v>
+      </c>
+      <c r="E84" s="14">
+        <v>60</v>
+      </c>
+      <c r="F84" s="14">
+        <v>150</v>
+      </c>
+      <c r="G84" s="14">
+        <v>3</v>
+      </c>
+      <c r="H84" s="14">
+        <v>180</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="962" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26F843E6-E690-489A-B3A3-64107046BB83}"/>
+  <xr:revisionPtr revIDLastSave="974" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A2FDC82-AFF1-4229-897E-B131B38DE098}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="180">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -572,6 +572,9 @@
   </si>
   <si>
     <t>29.10.2026</t>
+  </si>
+  <si>
+    <t>30.10.2026</t>
   </si>
 </sst>
 </file>
@@ -852,10 +855,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4917,25 +4916,47 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+      <c r="A85" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B85" s="14">
+        <v>420</v>
+      </c>
+      <c r="C85" s="14">
+        <v>30</v>
+      </c>
+      <c r="D85" s="14">
+        <v>90</v>
+      </c>
+      <c r="E85" s="14">
+        <v>60</v>
+      </c>
+      <c r="F85" s="14">
+        <v>300</v>
+      </c>
+      <c r="G85" s="14">
+        <v>6</v>
+      </c>
+      <c r="H85" s="14">
+        <v>120</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="974" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A2FDC82-AFF1-4229-897E-B131B38DE098}"/>
+  <xr:revisionPtr revIDLastSave="985" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A48CF14C-2E29-4FD1-AD22-DCF726BBAE97}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="181">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -575,6 +575,9 @@
   </si>
   <si>
     <t>30.10.2026</t>
+  </si>
+  <si>
+    <t>31.10.2026</t>
   </si>
 </sst>
 </file>
@@ -855,6 +858,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4960,25 +4967,47 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="15" t="str">
+      <c r="A86" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B86" s="14">
+        <v>420</v>
+      </c>
+      <c r="C86" s="14">
+        <v>30</v>
+      </c>
+      <c r="D86" s="14">
+        <v>90</v>
+      </c>
+      <c r="E86" s="14">
+        <v>60</v>
+      </c>
+      <c r="F86" s="14">
+        <v>200</v>
+      </c>
+      <c r="G86" s="14">
+        <v>4</v>
+      </c>
+      <c r="H86" s="14">
+        <v>120</v>
+      </c>
+      <c r="I86" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J86" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M86" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N86" s="17"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
